--- a/iron_oxo_DDCASPT2/iron_VDZP_SHAP.xlsx
+++ b/iron_oxo_DDCASPT2/iron_VDZP_SHAP.xlsx
@@ -450,7 +450,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.0004147835734525503</v>
+        <v>0.0004080343924632725</v>
       </c>
     </row>
     <row r="3">
@@ -463,7 +463,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.0002908560973987411</v>
+        <v>0.0002937742343905163</v>
       </c>
     </row>
     <row r="4">
@@ -476,7 +476,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.0002254040881591021</v>
+        <v>0.0002119186823377071</v>
       </c>
     </row>
     <row r="5">
@@ -489,7 +489,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.0001621271885981359</v>
+        <v>0.0001614601350042751</v>
       </c>
     </row>
     <row r="6">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.0001340690978451755</v>
+        <v>0.0001364980053442519</v>
       </c>
     </row>
     <row r="7">
@@ -515,7 +515,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.0001234474159007336</v>
+        <v>0.0001215044898435016</v>
       </c>
     </row>
     <row r="8">
@@ -528,33 +528,33 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.0001176476931310785</v>
+        <v>0.0001122057192757378</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>22</v>
+        <v>51</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>h$_{s}$</t>
+          <t>$(\eta_{r})_{1}$</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.000109611698848675</v>
+        <v>0.0001117880460234586</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>$(\eta_{r})_{1}$</t>
+          <t>h$_{s}$</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.0001092924295970475</v>
+        <v>0.0001065950484323381</v>
       </c>
     </row>
     <row r="11">
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>7.583337057740694e-05</v>
+        <v>7.663157758549456e-05</v>
       </c>
     </row>
     <row r="12">
@@ -580,59 +580,59 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>7.030886905455172e-05</v>
+        <v>7.047296814325301e-05</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>97</v>
+        <v>57</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>$(\langle rr \vert rr \rangle)_{3}$</t>
+          <t>$(\omega_{r})_{2}$</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5.540110250131223e-05</v>
+        <v>6.141972375091393e-05</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>$(\omega_{r})_{2}$</t>
+          <t>$\eta_{s}$</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>5.528857922024196e-05</v>
+        <v>5.44783197635085e-05</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>40</v>
+        <v>97</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>$F_{s}^{\text{SCF}}$</t>
+          <t>$(\langle rr \vert rr \rangle)_{3}$</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>5.3907237382785e-05</v>
+        <v>5.305392700417205e-05</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>$\omega_{s}$</t>
+          <t>$F_{s}^{\text{SCF}}$</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>5.067261043112274e-05</v>
+        <v>5.167774738282874e-05</v>
       </c>
     </row>
     <row r="17">
@@ -645,20 +645,20 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>5.022533929130881e-05</v>
+        <v>4.950112136721745e-05</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>$\eta_{s}$</t>
+          <t>$\omega_{s}$</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>5.010879139527134e-05</v>
+        <v>4.922825303591864e-05</v>
       </c>
     </row>
     <row r="19">
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>4.894964012305951e-05</v>
+        <v>4.917394807643284e-05</v>
       </c>
     </row>
     <row r="20">
@@ -684,72 +684,72 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4.854578504549892e-05</v>
+        <v>4.801385830860042e-05</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>$(\omega_{r})_{1}$</t>
+          <t>$(\omega_{p})_{2}$</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>4.613033188808599e-05</v>
+        <v>4.755070541347143e-05</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>$(\omega_{p})_{2}$</t>
+          <t>$F_{q}^{\text{SCF}}$</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>4.578931506235848e-05</v>
+        <v>4.632066149656919e-05</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>$F_{q}^{\text{SCF}}$</t>
+          <t>$(\omega_{r})_{1}$</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>4.315669946392124e-05</v>
+        <v>4.389596555345947e-05</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>13</v>
+        <v>73</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>h$_{qs}$</t>
+          <t>$\langle ss \vert ss \rangle$</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>4.272819666856654e-05</v>
+        <v>4.26705938156163e-05</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>73</v>
+        <v>13</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>$\langle ss \vert ss \rangle$</t>
+          <t>h$_{qs}$</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>3.974723130416576e-05</v>
+        <v>4.122513528815192e-05</v>
       </c>
     </row>
     <row r="26">
@@ -762,111 +762,111 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>3.738932487678512e-05</v>
+        <v>3.784153835647606e-05</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>(h$_{p}$)$_{0}$</t>
+          <t>$(\langle pq \vert qp \rangle)_{3}$</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>3.510612985424193e-05</v>
+        <v>3.55291399331767e-05</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>$F_{s}$</t>
+          <t>(h$_{p}$)$_{0}$</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>3.382181412097486e-05</v>
+        <v>3.527239028500712e-05</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>26</v>
+        <v>90</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>$type_3$</t>
+          <t>$(\langle pq \vert pq \rangle)_{2}$</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>3.352202308686562e-05</v>
+        <v>3.316828086149606e-05</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>(h$_{r}$)$_{2}$</t>
+          <t>$type_3$</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>3.269623720854638e-05</v>
+        <v>3.278027011177368e-05</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>99</v>
+        <v>42</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>$(\langle pq \vert qp \rangle)_{3}$</t>
+          <t>$F_{s}$</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>3.144901541523325e-05</v>
+        <v>3.247762752810695e-05</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>90</v>
+        <v>16</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>$(\langle pq \vert pq \rangle)_{2}$</t>
+          <t>(h$_{r}$)$_{2}$</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>3.066937712270076e-05</v>
+        <v>3.153055152801583e-05</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>78</v>
+        <v>98</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>$(\langle pq \vert rs \rangle)_{1}$</t>
+          <t>$(\langle pq \vert pq \rangle)_{3}$</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>2.972545353383824e-05</v>
+        <v>2.993228435911791e-05</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>98</v>
+        <v>78</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>$(\langle pq \vert pq \rangle)_{3}$</t>
+          <t>$(\langle pq \vert rs \rangle)_{1}$</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>2.924205366555794e-05</v>
+        <v>2.958940325897447e-05</v>
       </c>
     </row>
     <row r="35">
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>2.880797824305791e-05</v>
+        <v>2.930887722023225e-05</v>
       </c>
     </row>
     <row r="36">
@@ -892,7 +892,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>2.877772974373062e-05</v>
+        <v>2.916198534717055e-05</v>
       </c>
     </row>
     <row r="37">
@@ -905,7 +905,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>2.790245283656804e-05</v>
+        <v>2.764227186383333e-05</v>
       </c>
     </row>
     <row r="38">
@@ -918,7 +918,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>2.762249918575351e-05</v>
+        <v>2.682417206384235e-05</v>
       </c>
     </row>
     <row r="39">
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>2.555189428686214e-05</v>
+        <v>2.646545437618368e-05</v>
       </c>
     </row>
     <row r="40">
@@ -944,7 +944,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>2.500322265052189e-05</v>
+        <v>2.394572020859814e-05</v>
       </c>
     </row>
     <row r="41">
@@ -957,46 +957,46 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>2.467730605834434e-05</v>
+        <v>2.394450010476693e-05</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>(h$_{p}$)$_{3}$</t>
+          <t>$(F_{p}^{\text{SCF}})_{0}$</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>2.370859936291518e-05</v>
+        <v>2.290296438442565e-05</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>89</v>
+        <v>44</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>$(\langle rr \vert rr \rangle)_{2}$</t>
+          <t>$(F_{p}^{\text{SCF}})_{1}$</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>2.24425735379371e-05</v>
+        <v>2.285328041008015e-05</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>67</v>
+        <v>89</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>$(\eta_{r})_{3}$</t>
+          <t>$(\langle rr \vert rr \rangle)_{2}$</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>2.194952573238563e-05</v>
+        <v>2.233341331698436e-05</v>
       </c>
     </row>
     <row r="45">
@@ -1009,46 +1009,46 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>2.166553436885997e-05</v>
+        <v>2.220239315210031e-05</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>(h$_{p}$)$_{2}$</t>
+          <t>$(\omega_{p})_{3}$</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>2.161995342224316e-05</v>
+        <v>2.180471308145922e-05</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>44</v>
+        <v>3</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>$(F_{p}^{\text{SCF}})_{1}$</t>
+          <t>(h$_{p}$)$_{3}$</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>2.145205228392148e-05</v>
+        <v>2.179132008031015e-05</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>66</v>
+        <v>2</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>$(F_{r})_{3}$</t>
+          <t>(h$_{p}$)$_{2}$</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>2.131186471675095e-05</v>
+        <v>2.164594274935018e-05</v>
       </c>
     </row>
     <row r="49">
@@ -1061,137 +1061,137 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>2.127935391801965e-05</v>
+        <v>2.039955139384695e-05</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>$(\langle pq \vert pq \rangle)_{0}$</t>
+          <t>$(\eta_{r})_{3}$</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>2.083144159553002e-05</v>
+        <v>1.993328520752797e-05</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>28</v>
+        <v>66</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>$(F_{p}^{\text{SCF}})_{0}$</t>
+          <t>$(F_{r})_{3}$</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>2.048424288643049e-05</v>
+        <v>1.983460792449872e-05</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>$(\omega_{p})_{3}$</t>
+          <t>$(\langle pq \vert pq \rangle)_{0}$</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>2.019384158366014e-05</v>
+        <v>1.971439574649628e-05</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>48</v>
+        <v>75</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>$(F_{r}^{\text{SCF}})_{1}$</t>
+          <t>$(\langle pq \vert qp \rangle)_{0}$</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1.86468955907999e-05</v>
+        <v>1.855956520355063e-05</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>$type_1$</t>
+          <t>$(F_{r}^{\text{SCF}})_{1}$</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1.856037332654823e-05</v>
+        <v>1.78110364247115e-05</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>75</v>
+        <v>24</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>$(\langle pq \vert qp \rangle)_{0}$</t>
+          <t>$type_1$</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1.825175037009249e-05</v>
+        <v>1.744647852670322e-05</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>85</v>
+        <v>47</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>$(\langle rs \vert sr \rangle)_{1}$</t>
+          <t>$(\eta_{p})_{1}$</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1.782761198872627e-05</v>
+        <v>1.707840555065008e-05</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>21</v>
+        <v>85</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>(h$_{rs}$)$_{3}$</t>
+          <t>$(\langle rs \vert sr \rangle)_{1}$</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1.649151046863715e-05</v>
+        <v>1.647603822399645e-05</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>$(\omega_{p})_{1}$</t>
+          <t>(h$_{rs}$)$_{3}$</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1.614419651622889e-05</v>
+        <v>1.598483559341629e-05</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>58</v>
+        <v>100</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>$(F_{r})_{2}$</t>
+          <t>$(\langle rs\vert rs \rangle)_{3}$</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1.405739590167229e-05</v>
+        <v>1.569155782538025e-05</v>
       </c>
     </row>
     <row r="60">
@@ -1204,59 +1204,59 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1.398789803635251e-05</v>
+        <v>1.495993835072871e-05</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>93</v>
+        <v>45</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>$(\langle rs \vert sr \rangle)_{2}$</t>
+          <t>$(\omega_{p})_{1}$</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1.39204201783251e-05</v>
+        <v>1.495550431158292e-05</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>$(\langle rs\vert rs \rangle)_{2}$</t>
+          <t>$(\langle rs\vert rs \rangle)_{1}$</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1.383879591033324e-05</v>
+        <v>1.491700206973068e-05</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>$(\langle rs\vert rs \rangle)_{3}$</t>
+          <t>$(\langle rs\vert rs \rangle)_{2}$</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>1.377250676613535e-05</v>
+        <v>1.478481958730544e-05</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>$(\eta_{p})_{1}$</t>
+          <t>$(F_{r})_{2}$</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1.370057122698882e-05</v>
+        <v>1.400931294501829e-05</v>
       </c>
     </row>
     <row r="65">
@@ -1269,46 +1269,46 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1.364546250502321e-05</v>
+        <v>1.400675240002902e-05</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>$(\langle pq \vert qp \rangle)_{1}$</t>
+          <t>$(\langle rs \vert sr \rangle)_{2}$</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1.342526736476277e-05</v>
+        <v>1.375677908592226e-05</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>55</v>
+        <v>83</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>$(\eta_{p})_{2}$</t>
+          <t>$(\langle pq \vert qp \rangle)_{1}$</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1.341475258890273e-05</v>
+        <v>1.320369961672412e-05</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>84</v>
+        <v>55</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>$(\langle rs\vert rs \rangle)_{1}$</t>
+          <t>$(\eta_{p})_{2}$</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1.298724461177479e-05</v>
+        <v>1.266016880825566e-05</v>
       </c>
     </row>
     <row r="69">
@@ -1321,20 +1321,20 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1.257822143379857e-05</v>
+        <v>1.231795724595253e-05</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>81</v>
+        <v>60</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>$(\langle rr \vert rr \rangle)_{1}$</t>
+          <t>$(F_{p}^{\text{SCF}})_{3}$</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1.208708811872289e-05</v>
+        <v>1.10167276173681e-05</v>
       </c>
     </row>
     <row r="71">
@@ -1347,189 +1347,189 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1.206194002070736e-05</v>
+        <v>1.096282965528297e-05</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>$(F_{p}^{\text{SCF}})_{3}$</t>
+          <t>$(\langle rr \vert rr \rangle)_{0}$</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1.14480821947826e-05</v>
+        <v>1.007724216618407e-05</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>$(\langle rr \vert rr \rangle)_{0}$</t>
+          <t>$(\langle rr \vert rr \rangle)_{1}$</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>1.054587333829056e-05</v>
+        <v>9.806551112630138e-06</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>88</v>
+        <v>7</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>$(\langle pp \vert pp \rangle)_{2}$</t>
+          <t>(h$_{pq}$)$_{3}$</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>1.046330578617555e-05</v>
+        <v>9.535357170566663e-06</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>50</v>
+        <v>88</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>$(F_{r})_{1}$</t>
+          <t>$(\langle pp \vert pp \rangle)_{2}$</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>9.736810460318345e-06</v>
+        <v>9.359917496697704e-06</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>(h$_{pq}$)$_{3}$</t>
+          <t>(h$_{pq}$)$_{2}$</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>9.64952475843561e-06</v>
+        <v>9.114144217496836e-06</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>$(F_{p})_{0}$</t>
+          <t>$(F_{r})_{1}$</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>9.511353650007364e-06</v>
+        <v>8.805723862017477e-06</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>5</v>
+        <v>80</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>(h$_{pq}$)$_{1}$</t>
+          <t>$(\langle pp \vert pp \rangle)_{1}$</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>9.181144093710802e-06</v>
+        <v>8.364411757693862e-06</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>6</v>
+        <v>39</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>(h$_{pq}$)$_{2}$</t>
+          <t>$(\eta_{r})_{0}$</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>8.746495189779597e-06</v>
+        <v>8.334466711065487e-06</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>$(\langle rs \vert sr \rangle)_{0}$</t>
+          <t>$(\langle rs\vert rs \rangle)_{0}$</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>8.669908306326509e-06</v>
+        <v>7.959091047875861e-06</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>$(F_{r}^{\text{SCF}})_{0}$</t>
+          <t>(h$_{rs}$)$_{2}$</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>8.60787769624548e-06</v>
+        <v>7.880376180955099e-06</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>$(\langle rs\vert rs \rangle)_{0}$</t>
+          <t>$(F_{r}^{\text{SCF}})_{0}$</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>8.57747991604444e-06</v>
+        <v>7.837873264214719e-06</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>$(\langle pp \vert pp \rangle)_{1}$</t>
+          <t>$(\langle rs \vert sr \rangle)_{0}$</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>7.58459754194243e-06</v>
+        <v>7.588711741372041e-06</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>$(\eta_{r})_{0}$</t>
+          <t>$(F_{p})_{0}$</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>7.424434096315851e-06</v>
+        <v>7.485780512140339e-06</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>(h$_{rs}$)$_{2}$</t>
+          <t>(h$_{r}$)$_{0}$</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>6.614931994552312e-06</v>
+        <v>6.700486675177587e-06</v>
       </c>
     </row>
     <row r="86">
@@ -1542,215 +1542,215 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>6.446747283783063e-06</v>
+        <v>6.260973548352496e-06</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>10</v>
+        <v>87</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>(h$_{pr}$)$_{2}$</t>
+          <t>$(\langle pq \vert sr \rangle)_{2}$</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>6.103454588417964e-06</v>
+        <v>6.023349035740716e-06</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>(h$_{r}$)$_{0}$</t>
+          <t>(h$_{pq}$)$_{1}$</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>5.285468178272739e-06</v>
+        <v>5.947844864777375e-06</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>8</v>
+        <v>79</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>(h$_{pr}$)$_{0}$</t>
+          <t>$(\langle pq \vert sr \rangle)_{1}$</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>5.130619698858806e-06</v>
+        <v>5.863234946399054e-06</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>(h$_{rs}$)$_{0}$</t>
+          <t>(h$_{pr}$)$_{0}$</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>4.861943880478145e-06</v>
+        <v>5.388410045208922e-06</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>86</v>
+        <v>9</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>$(\langle pq \vert rs \rangle)_{2}$</t>
+          <t>(h$_{pr}$)$_{1}$</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>4.702387727635698e-06</v>
+        <v>4.564239578857892e-06</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>(h$_{pr}$)$_{1}$</t>
+          <t>(h$_{pr}$)$_{2}$</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>4.542776859953937e-06</v>
+        <v>4.549073810956814e-06</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>4</v>
+        <v>69</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>(h$_{pq}$)$_{0}$</t>
+          <t>$(\langle pq \vert sr \rangle)_{0}$</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>4.358596413610488e-06</v>
+        <v>4.324461662719277e-06</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>94</v>
+        <v>4</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>$(\langle pq \vert rs \rangle)_{3}$</t>
+          <t>(h$_{pq}$)$_{0}$</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>4.044607385059703e-06</v>
+        <v>4.285683886468262e-06</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>11</v>
+        <v>95</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>(h$_{pr}$)$_{3}$</t>
+          <t>$(\langle pq \vert sr \rangle)_{3}$</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>3.371106522828484e-06</v>
+        <v>4.189862068216239e-06</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>38</v>
+        <v>94</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>$(F_{r})_{0}$</t>
+          <t>$(\langle pq \vert rs \rangle)_{3}$</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>2.74040683384151e-06</v>
+        <v>4.007402025009748e-06</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>68</v>
+        <v>11</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>$(\langle pq \vert rs \rangle)_{0}$</t>
+          <t>(h$_{pr}$)$_{3}$</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>1.565196796589627e-06</v>
+        <v>3.073715341529227e-06</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>31</v>
+        <v>86</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>$(\eta_{p})_{0}$</t>
+          <t>$(\langle pq \vert rs \rangle)_{2}$</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>1.530204272353371e-06</v>
+        <v>3.009965674228105e-06</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>87</v>
+        <v>18</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>$(\langle pq \vert sr \rangle)_{2}$</t>
+          <t>(h$_{rs}$)$_{0}$</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>2.231152104564879e-07</v>
+        <v>2.842069546856361e-06</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>69</v>
+        <v>38</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>$(\langle pq \vert sr \rangle)_{0}$</t>
+          <t>$(F_{r})_{0}$</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>2.139017410912953e-07</v>
+        <v>2.432412408500608e-06</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>79</v>
+        <v>31</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>$(\langle pq \vert sr \rangle)_{1}$</t>
+          <t>$(\eta_{p})_{0}$</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>2.002322563337279e-07</v>
+        <v>1.539797929844305e-06</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>95</v>
+        <v>68</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>$(\langle pq \vert sr \rangle)_{3}$</t>
+          <t>$(\langle pq \vert rs \rangle)_{0}$</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>1.723540907865675e-07</v>
+        <v>1.480043044652904e-06</v>
       </c>
     </row>
     <row r="103">
@@ -1763,7 +1763,7 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>2.709181034506403e-08</v>
+        <v>2.704421221089428e-08</v>
       </c>
     </row>
   </sheetData>
